--- a/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
+++ b/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
@@ -3514,13 +3514,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{264BB595-6838-4A7A-ACA8-3EE4CA4080D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CDED5EA-3B0B-4992-A96B-B20A3B9CF625}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71E3F197-262C-4595-A619-1DFCD9437E4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC28B287-10E6-4CA4-82DB-10106C6F436C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59EB8ECC-C48C-40D2-A454-744751A9C81C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{921DD151-BAFA-4AC7-B0A4-18377B0DAAA7}"/>
 </file>